--- a/output/第10期計画_事業所調査の照会票と確定値管理表.xlsx
+++ b/output/第10期計画_事業所調査の照会票と確定値管理表.xlsx
@@ -3040,7 +3040,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>20.4％</t>
+          <t>20.2％</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>20.4％</t>
+          <t>20.2％</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>20.4％</t>
+          <t>20.2％</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>98票中20票。提出元の偏りの影響を受けない設問である</t>
+          <t>99票中20票。提出元の偏りの影響を受けない設問である</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
     <row r="16" ht="39" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>注1）「確定」は照会の結果によらず値が変わらないものである。No.3（訪問介護員等181人）とNo.7（H12の20.4％）は公表画面及び設問の性質により確定している。注2）「決定待ち」は事業者の回答ではなく、発注者の集計方法の決定により確定するものである。注3）本表の値が変われば05シートの箇所を更新する。注4）本表は照会の発出後に「回答後の値」欄を埋めて更新する。現時点では回答前の値のみが入っている。</t>
+          <t>注1）「確定」は照会の結果によらず値が変わらないものである。No.3（訪問介護員等181人）とNo.7（H12の20.2％）は公表画面及び設問の性質により確定している。注2）「決定待ち」は事業者の回答ではなく、発注者の集計方法の決定により確定するものである。注3）本表の値が変われば05シートの箇所を更新する。注4）本表は照会の発出後に「回答後の値」欄を埋めて更新する。現時点では回答前の値のみが入っている。</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）作業量「大」の⑨（施設の定員）は、資料提供依頼No.7（事業所・施設の定員と稼働の実績）の受領を要する。事業者への照会だけでは確定しない。注2）代表KPIの基準値のうち、本照会により変わりうるのはH13（職種別従事者数）のみである。H13は見える化M2系列を用いるため、調査の回答が変わっても基準値は変わらない。注3）H12（20.4％）は在宅生活改善調査の利用者票によるが、確定値表No.7のとおり照会の影響を受けない。</t>
+          <t>注1）作業量「大」の⑨（施設の定員）は、資料提供依頼No.7（事業所・施設の定員と稼働の実績）の受領を要する。事業者への照会だけでは確定しない。注2）代表KPIの基準値のうち、本照会により変わりうるのはH13（職種別従事者数）のみである。H13は見える化M2系列を用いるため、調査の回答が変わっても基準値は変わらない。注3）H12（20.2％）は在宅生活改善調査の利用者票によるが、確定値表No.7のとおり照会の影響を受けない。</t>
         </is>
       </c>
     </row>
